--- a/examples/SmallDrugCombo_Zhou_CellChemBio_2026/raw_data/Untreated.xlsx
+++ b/examples/SmallDrugCombo_Zhou_CellChemBio_2026/raw_data/Untreated.xlsx
@@ -18,16 +18,16 @@
     <t>vehicle</t>
   </si>
   <si>
-    <t>CL131438</t>
+    <t>CL00100</t>
   </si>
   <si>
-    <t>CL131891</t>
+    <t>CL00101</t>
   </si>
   <si>
-    <t>CL129757</t>
+    <t>CL00102</t>
   </si>
   <si>
-    <t>CL130742</t>
+    <t>CL00103</t>
   </si>
 </sst>
 </file>
